--- a/docs/画面一覧・機能一覧.xlsx
+++ b/docs/画面一覧・機能一覧.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改訂履歴" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'画面一覧'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'機能一覧'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'画面一覧'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'機能一覧'!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'画面項目定義'!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'改訂履歴'!$A$1:$D$2</definedName>
   </definedNames>
@@ -37,7 +37,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -47,16 +47,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,18 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -538,51 +522,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SC-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>メニュー</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>横断</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>起動時に表示し、取込・マッチング・修正・出力の各画面への入口となる</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>sys-staff</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>管理者要件 R-01。設計は sys-staff が行う</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -593,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -660,48 +601,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>メニュー表示</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>横断</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>SC-01</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>各機能への入口を提供する</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>採用</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-30 10:57:45</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
